--- a/Luban/DataTables/Datas/Entity/单位表.xlsx
+++ b/Luban/DataTables/Datas/Entity/单位表.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="60">
   <si>
     <t>##</t>
   </si>
@@ -222,9 +222,6 @@
   </si>
   <si>
     <t>Entities/Player/Sp_Player_Swordman.png</t>
-  </si>
-  <si>
-    <t>Entities/Player/Template_100001.png</t>
   </si>
   <si>
     <t>test</t>
@@ -1302,7 +1299,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:W15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -1310,7 +1307,8 @@
     <col min="3" max="3" width="11.1916666666667" customWidth="1"/>
     <col min="4" max="4" width="10.975" customWidth="1"/>
     <col min="5" max="5" width="14.6666666666667" customWidth="1"/>
-    <col min="6" max="8" width="11.1916666666667" customWidth="1"/>
+    <col min="6" max="6" width="29.0166666666667" customWidth="1"/>
+    <col min="7" max="8" width="11.1916666666667" customWidth="1"/>
     <col min="10" max="10" width="9.23333333333333" customWidth="1"/>
     <col min="11" max="11" width="10.5416666666667" customWidth="1"/>
     <col min="12" max="16" width="9" customWidth="1"/>
@@ -1558,111 +1556,73 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" ht="42.75" spans="1:23">
-      <c r="A5" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="18">
-        <v>100002</v>
-      </c>
-      <c r="C5" s="18">
-        <v>100002</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" s="18">
-        <v>100002</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5" s="19">
-        <v>5</v>
-      </c>
-      <c r="H5" s="18">
-        <v>0</v>
-      </c>
-      <c r="I5" s="18">
-        <v>0</v>
-      </c>
-      <c r="J5" s="18">
-        <v>0</v>
-      </c>
-      <c r="K5" s="18">
-        <v>0</v>
-      </c>
-      <c r="L5" s="18">
-        <v>6</v>
-      </c>
-      <c r="M5" s="18">
-        <v>10</v>
-      </c>
-      <c r="N5" s="18">
-        <v>0</v>
-      </c>
-      <c r="O5" s="18">
-        <v>25</v>
-      </c>
-      <c r="P5" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="18">
-        <v>0</v>
-      </c>
-      <c r="R5" s="18">
-        <v>0</v>
-      </c>
-      <c r="S5" s="18">
-        <v>0</v>
-      </c>
-      <c r="T5" s="18">
-        <v>0</v>
-      </c>
+    <row r="5" spans="1:23">
+      <c r="A5" s="20"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="18"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="18"/>
+      <c r="Q5" s="18"/>
+      <c r="R5" s="18"/>
+      <c r="S5" s="18"/>
+      <c r="T5" s="18"/>
     </row>
     <row r="6" ht="42.75" spans="1:23">
-      <c r="A6" s="18"/>
+      <c r="A6" s="20" t="s">
+        <v>52</v>
+      </c>
       <c r="B6" s="18">
-        <v>100003</v>
+        <v>500001</v>
       </c>
       <c r="C6" s="18">
-        <v>100003</v>
+        <v>500001</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E6" s="18">
-        <v>100003</v>
+        <v>500001</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G6" s="19">
         <v>5</v>
       </c>
       <c r="H6" s="18">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I6" s="18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J6" s="18">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K6" s="18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L6" s="18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M6" s="18">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N6" s="18">
         <v>0</v>
       </c>
       <c r="O6" s="18">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="P6" s="18">
         <v>0</v>
@@ -1679,173 +1639,241 @@
       <c r="T6" s="18">
         <v>0</v>
       </c>
+      <c r="V6" s="20">
+        <v>10002</v>
+      </c>
+      <c r="W6" s="18">
+        <v>100001</v>
+      </c>
     </row>
-    <row r="7" ht="42.75" spans="1:23">
-      <c r="A7" s="18"/>
+    <row r="7" ht="57" spans="1:23">
+      <c r="A7" s="20" t="s">
+        <v>52</v>
+      </c>
       <c r="B7" s="18">
-        <v>100004</v>
+        <v>500002</v>
       </c>
       <c r="C7" s="18">
-        <v>100004</v>
+        <v>500002</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E7" s="18">
-        <v>100004</v>
+        <v>500002</v>
       </c>
       <c r="F7" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7" s="19">
+        <v>4</v>
+      </c>
+      <c r="H7" s="18">
+        <v>1</v>
+      </c>
+      <c r="I7" s="18">
+        <v>2</v>
+      </c>
+      <c r="J7" s="18">
+        <v>0</v>
+      </c>
+      <c r="K7" s="18">
+        <v>1</v>
+      </c>
+      <c r="L7" s="18">
+        <v>7</v>
+      </c>
+      <c r="M7" s="18">
+        <v>0</v>
+      </c>
+      <c r="N7" s="18">
+        <v>0</v>
+      </c>
+      <c r="O7" s="18">
+        <v>0</v>
+      </c>
+      <c r="P7" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="18">
+        <v>0</v>
+      </c>
+      <c r="R7" s="18">
+        <v>0</v>
+      </c>
+      <c r="S7" s="18">
+        <v>0</v>
+      </c>
+      <c r="T7" s="18">
+        <v>0</v>
+      </c>
+      <c r="V7" s="20">
+        <v>10002</v>
+      </c>
+      <c r="W7" s="18">
+        <v>100001</v>
+      </c>
+    </row>
+    <row r="8" ht="57" spans="1:23">
+      <c r="A8" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="G7" s="19">
-        <v>5</v>
-      </c>
-      <c r="H7" s="18">
-        <v>0</v>
-      </c>
-      <c r="I7" s="18">
-        <v>0</v>
-      </c>
-      <c r="J7" s="18">
-        <v>0</v>
-      </c>
-      <c r="K7" s="18">
-        <v>0</v>
-      </c>
-      <c r="L7" s="18">
-        <v>6</v>
-      </c>
-      <c r="M7" s="18">
-        <v>10</v>
-      </c>
-      <c r="N7" s="18">
-        <v>0</v>
-      </c>
-      <c r="O7" s="18">
-        <v>25</v>
-      </c>
-      <c r="P7" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="18">
-        <v>0</v>
-      </c>
-      <c r="R7" s="18">
-        <v>0</v>
-      </c>
-      <c r="S7" s="18">
-        <v>0</v>
-      </c>
-      <c r="T7" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="42.75" spans="1:23">
-      <c r="A8" s="18"/>
       <c r="B8" s="18">
-        <v>100005</v>
+        <v>500003</v>
       </c>
       <c r="C8" s="18">
-        <v>100005</v>
+        <v>500003</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E8" s="18">
-        <v>100005</v>
+        <v>500003</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G8" s="19">
         <v>5</v>
       </c>
       <c r="H8" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="18">
         <v>0</v>
       </c>
       <c r="K8" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="18">
+        <v>4</v>
+      </c>
+      <c r="M8" s="18">
+        <v>0</v>
+      </c>
+      <c r="N8" s="18">
+        <v>0</v>
+      </c>
+      <c r="O8" s="18">
+        <v>0</v>
+      </c>
+      <c r="P8" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="18">
+        <v>0</v>
+      </c>
+      <c r="R8" s="18">
+        <v>0</v>
+      </c>
+      <c r="S8" s="18">
+        <v>0</v>
+      </c>
+      <c r="T8" s="18">
+        <v>0</v>
+      </c>
+      <c r="V8" s="20">
+        <v>10002</v>
+      </c>
+      <c r="W8" s="18">
+        <v>100001</v>
+      </c>
+    </row>
+    <row r="9" ht="57" spans="1:23">
+      <c r="A9" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="18">
+        <v>500004</v>
+      </c>
+      <c r="C9" s="18">
+        <v>500004</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="18">
+        <v>500004</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="19">
+        <v>4</v>
+      </c>
+      <c r="H9" s="18">
+        <v>0</v>
+      </c>
+      <c r="I9" s="18">
+        <v>1</v>
+      </c>
+      <c r="J9" s="18">
+        <v>0</v>
+      </c>
+      <c r="K9" s="18">
+        <v>1</v>
+      </c>
+      <c r="L9" s="18">
         <v>6</v>
       </c>
-      <c r="M8" s="18">
-        <v>10</v>
-      </c>
-      <c r="N8" s="18">
-        <v>0</v>
-      </c>
-      <c r="O8" s="18">
-        <v>25</v>
-      </c>
-      <c r="P8" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="18">
-        <v>0</v>
-      </c>
-      <c r="R8" s="18">
-        <v>0</v>
-      </c>
-      <c r="S8" s="18">
-        <v>0</v>
-      </c>
-      <c r="T8" s="18">
-        <v>0</v>
+      <c r="M9" s="18">
+        <v>0</v>
+      </c>
+      <c r="N9" s="18">
+        <v>0</v>
+      </c>
+      <c r="O9" s="18">
+        <v>0</v>
+      </c>
+      <c r="P9" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="18">
+        <v>0</v>
+      </c>
+      <c r="R9" s="18">
+        <v>0</v>
+      </c>
+      <c r="S9" s="18">
+        <v>0</v>
+      </c>
+      <c r="T9" s="18">
+        <v>0</v>
+      </c>
+      <c r="V9" s="20">
+        <v>10002</v>
+      </c>
+      <c r="W9" s="18">
+        <v>100001</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
-      <c r="A9" s="20"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="18"/>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
-      <c r="P9" s="18"/>
-      <c r="Q9" s="18"/>
-      <c r="R9" s="18"/>
-      <c r="S9" s="18"/>
-      <c r="T9" s="18"/>
-    </row>
-    <row r="10" ht="42.75" spans="1:23">
+    <row r="10" ht="57" spans="1:23">
       <c r="A10" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="18">
+        <v>500005</v>
+      </c>
+      <c r="C10" s="18">
+        <v>500005</v>
+      </c>
+      <c r="D10" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="B10" s="18">
-        <v>500001</v>
-      </c>
-      <c r="C10" s="18">
-        <v>500001</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>54</v>
-      </c>
       <c r="E10" s="18">
-        <v>500001</v>
+        <v>500005</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G10" s="19">
         <v>5</v>
       </c>
       <c r="H10" s="18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" s="18">
         <v>1</v>
@@ -1857,7 +1885,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M10" s="18">
         <v>0</v>
@@ -1892,31 +1920,31 @@
     </row>
     <row r="11" ht="57" spans="1:23">
       <c r="A11" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="18">
+        <v>500006</v>
+      </c>
+      <c r="C11" s="18">
+        <v>500006</v>
+      </c>
+      <c r="D11" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="18">
-        <v>500002</v>
-      </c>
-      <c r="C11" s="18">
-        <v>500002</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>54</v>
-      </c>
       <c r="E11" s="18">
-        <v>500002</v>
+        <v>500006</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G11" s="19">
         <v>4</v>
       </c>
       <c r="H11" s="18">
+        <v>0</v>
+      </c>
+      <c r="I11" s="18">
         <v>1</v>
-      </c>
-      <c r="I11" s="18">
-        <v>2</v>
       </c>
       <c r="J11" s="18">
         <v>0</v>
@@ -1925,7 +1953,7 @@
         <v>1</v>
       </c>
       <c r="L11" s="18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M11" s="18">
         <v>0</v>
@@ -1958,228 +1986,29 @@
         <v>100001</v>
       </c>
     </row>
-    <row r="12" ht="57" spans="1:23">
-      <c r="A12" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" s="18">
-        <v>500003</v>
-      </c>
-      <c r="C12" s="18">
-        <v>500003</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" s="18">
-        <v>500003</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="G12" s="19">
-        <v>5</v>
-      </c>
-      <c r="H12" s="18">
-        <v>1</v>
-      </c>
-      <c r="I12" s="18">
-        <v>1</v>
-      </c>
-      <c r="J12" s="18">
-        <v>0</v>
-      </c>
-      <c r="K12" s="18">
-        <v>1</v>
-      </c>
-      <c r="L12" s="18">
-        <v>4</v>
-      </c>
-      <c r="M12" s="18">
-        <v>0</v>
-      </c>
-      <c r="N12" s="18">
-        <v>0</v>
-      </c>
-      <c r="O12" s="18">
-        <v>0</v>
-      </c>
-      <c r="P12" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="18">
-        <v>0</v>
-      </c>
-      <c r="R12" s="18">
-        <v>0</v>
-      </c>
-      <c r="S12" s="18">
-        <v>0</v>
-      </c>
-      <c r="T12" s="18">
-        <v>0</v>
-      </c>
-      <c r="V12" s="20">
-        <v>10002</v>
-      </c>
-      <c r="W12" s="18">
-        <v>100001</v>
-      </c>
-    </row>
-    <row r="13" ht="57" spans="1:23">
-      <c r="A13" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" s="18">
-        <v>500004</v>
-      </c>
-      <c r="C13" s="18">
-        <v>500004</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" s="18">
-        <v>500004</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="G13" s="19">
-        <v>4</v>
-      </c>
-      <c r="H13" s="18">
-        <v>0</v>
-      </c>
-      <c r="I13" s="18">
-        <v>1</v>
-      </c>
-      <c r="J13" s="18">
-        <v>0</v>
-      </c>
-      <c r="K13" s="18">
-        <v>1</v>
-      </c>
-      <c r="L13" s="18">
-        <v>6</v>
-      </c>
-      <c r="M13" s="18">
-        <v>0</v>
-      </c>
-      <c r="N13" s="18">
-        <v>0</v>
-      </c>
-      <c r="O13" s="18">
-        <v>0</v>
-      </c>
-      <c r="P13" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="18">
-        <v>0</v>
-      </c>
-      <c r="R13" s="18">
-        <v>0</v>
-      </c>
-      <c r="S13" s="18">
-        <v>0</v>
-      </c>
-      <c r="T13" s="18">
-        <v>0</v>
-      </c>
-      <c r="V13" s="20">
-        <v>10002</v>
-      </c>
-      <c r="W13" s="18">
-        <v>100001</v>
-      </c>
-    </row>
-    <row r="14" ht="57" spans="1:23">
-      <c r="A14" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="B14" s="18">
-        <v>500005</v>
-      </c>
-      <c r="C14" s="18">
-        <v>500005</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" s="18">
-        <v>500005</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14" s="19">
-        <v>5</v>
-      </c>
-      <c r="H14" s="18">
-        <v>0</v>
-      </c>
-      <c r="I14" s="18">
-        <v>1</v>
-      </c>
-      <c r="J14" s="18">
-        <v>0</v>
-      </c>
-      <c r="K14" s="18">
-        <v>1</v>
-      </c>
-      <c r="L14" s="18">
-        <v>9</v>
-      </c>
-      <c r="M14" s="18">
-        <v>0</v>
-      </c>
-      <c r="N14" s="18">
-        <v>0</v>
-      </c>
-      <c r="O14" s="18">
-        <v>0</v>
-      </c>
-      <c r="P14" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="18">
-        <v>0</v>
-      </c>
-      <c r="R14" s="18">
-        <v>0</v>
-      </c>
-      <c r="S14" s="18">
-        <v>0</v>
-      </c>
-      <c r="T14" s="18">
-        <v>0</v>
-      </c>
-      <c r="V14" s="20">
-        <v>10002</v>
-      </c>
-      <c r="W14" s="18">
-        <v>100001</v>
-      </c>
+    <row r="12" spans="1:23">
+      <c r="R12" s="18"/>
+      <c r="S12" s="18"/>
+      <c r="T12" s="18"/>
     </row>
     <row r="15" ht="57" spans="1:23">
       <c r="A15" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="18">
+        <v>500007</v>
+      </c>
+      <c r="C15" s="18">
+        <v>500007</v>
+      </c>
+      <c r="D15" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="18">
-        <v>500006</v>
-      </c>
-      <c r="C15" s="18">
-        <v>500006</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>54</v>
-      </c>
       <c r="E15" s="18">
-        <v>500006</v>
+        <v>500007</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G15" s="19">
         <v>4</v>
@@ -2223,81 +2052,8 @@
       <c r="T15" s="18">
         <v>0</v>
       </c>
-      <c r="V15" s="20">
-        <v>10002</v>
-      </c>
+      <c r="V15" s="18"/>
       <c r="W15" s="18">
-        <v>100001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23">
-      <c r="R16" s="18"/>
-      <c r="S16" s="18"/>
-      <c r="T16" s="18"/>
-    </row>
-    <row r="19" ht="57" spans="1:23">
-      <c r="A19" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="B19" s="18">
-        <v>500007</v>
-      </c>
-      <c r="C19" s="18">
-        <v>500007</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="E19" s="18">
-        <v>500007</v>
-      </c>
-      <c r="F19" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="G19" s="19">
-        <v>4</v>
-      </c>
-      <c r="H19" s="18">
-        <v>0</v>
-      </c>
-      <c r="I19" s="18">
-        <v>1</v>
-      </c>
-      <c r="J19" s="18">
-        <v>0</v>
-      </c>
-      <c r="K19" s="18">
-        <v>1</v>
-      </c>
-      <c r="L19" s="18">
-        <v>6</v>
-      </c>
-      <c r="M19" s="18">
-        <v>0</v>
-      </c>
-      <c r="N19" s="18">
-        <v>0</v>
-      </c>
-      <c r="O19" s="18">
-        <v>0</v>
-      </c>
-      <c r="P19" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="18">
-        <v>0</v>
-      </c>
-      <c r="R19" s="18">
-        <v>0</v>
-      </c>
-      <c r="S19" s="18">
-        <v>0</v>
-      </c>
-      <c r="T19" s="18">
-        <v>0</v>
-      </c>
-      <c r="V19" s="18"/>
-      <c r="W19" s="18">
         <v>100002</v>
       </c>
     </row>
@@ -2306,7 +2062,7 @@
     <mergeCell ref="G1:T1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D19 D4:D15">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4 D15 D5:D11">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>

--- a/Luban/DataTables/Datas/Entity/单位表.xlsx
+++ b/Luban/DataTables/Datas/Entity/单位表.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="56">
   <si>
     <t>##</t>
   </si>
@@ -230,22 +230,10 @@
     <t>敌方模板</t>
   </si>
   <si>
-    <t>Entities/Enemies/Sp_Enemy_Bat.png</t>
+    <t>Entities/Enemies/Sp_Enemy_Troll.png</t>
   </si>
   <si>
     <t>Entities/Enemies/Goblin/T_Goblin_02.png</t>
-  </si>
-  <si>
-    <t>Entities/Enemies/Goblin/T_Goblin_03.png</t>
-  </si>
-  <si>
-    <t>Entities/Enemies/Boss/FacelessContractor.png</t>
-  </si>
-  <si>
-    <t>Entities/Enemies/Goblin/T_Goblin_05.png</t>
-  </si>
-  <si>
-    <t>Entities/Enemies/Goblin/T_Goblin_06.png</t>
   </si>
 </sst>
 </file>
@@ -1299,8 +1287,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:W7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="19.45" customWidth="1"/>
@@ -1494,7 +1482,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" ht="57" spans="1:23">
+    <row r="4" ht="28.5" spans="1:23">
       <c r="A4" s="18" t="s">
         <v>49</v>
       </c>
@@ -1578,7 +1566,7 @@
       <c r="S5" s="18"/>
       <c r="T5" s="18"/>
     </row>
-    <row r="6" ht="42.75" spans="1:23">
+    <row r="6" ht="28.5" spans="1:23">
       <c r="A6" s="20" t="s">
         <v>52</v>
       </c>
@@ -1646,7 +1634,7 @@
         <v>100001</v>
       </c>
     </row>
-    <row r="7" ht="57" spans="1:23">
+    <row r="7" ht="28.5" spans="1:23">
       <c r="A7" s="20" t="s">
         <v>52</v>
       </c>
@@ -1712,349 +1700,6 @@
       </c>
       <c r="W7" s="18">
         <v>100001</v>
-      </c>
-    </row>
-    <row r="8" ht="57" spans="1:23">
-      <c r="A8" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="18">
-        <v>500003</v>
-      </c>
-      <c r="C8" s="18">
-        <v>500003</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" s="18">
-        <v>500003</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8" s="19">
-        <v>5</v>
-      </c>
-      <c r="H8" s="18">
-        <v>1</v>
-      </c>
-      <c r="I8" s="18">
-        <v>1</v>
-      </c>
-      <c r="J8" s="18">
-        <v>0</v>
-      </c>
-      <c r="K8" s="18">
-        <v>1</v>
-      </c>
-      <c r="L8" s="18">
-        <v>4</v>
-      </c>
-      <c r="M8" s="18">
-        <v>0</v>
-      </c>
-      <c r="N8" s="18">
-        <v>0</v>
-      </c>
-      <c r="O8" s="18">
-        <v>0</v>
-      </c>
-      <c r="P8" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="18">
-        <v>0</v>
-      </c>
-      <c r="R8" s="18">
-        <v>0</v>
-      </c>
-      <c r="S8" s="18">
-        <v>0</v>
-      </c>
-      <c r="T8" s="18">
-        <v>0</v>
-      </c>
-      <c r="V8" s="20">
-        <v>10002</v>
-      </c>
-      <c r="W8" s="18">
-        <v>100001</v>
-      </c>
-    </row>
-    <row r="9" ht="57" spans="1:23">
-      <c r="A9" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" s="18">
-        <v>500004</v>
-      </c>
-      <c r="C9" s="18">
-        <v>500004</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="18">
-        <v>500004</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9" s="19">
-        <v>4</v>
-      </c>
-      <c r="H9" s="18">
-        <v>0</v>
-      </c>
-      <c r="I9" s="18">
-        <v>1</v>
-      </c>
-      <c r="J9" s="18">
-        <v>0</v>
-      </c>
-      <c r="K9" s="18">
-        <v>1</v>
-      </c>
-      <c r="L9" s="18">
-        <v>6</v>
-      </c>
-      <c r="M9" s="18">
-        <v>0</v>
-      </c>
-      <c r="N9" s="18">
-        <v>0</v>
-      </c>
-      <c r="O9" s="18">
-        <v>0</v>
-      </c>
-      <c r="P9" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="18">
-        <v>0</v>
-      </c>
-      <c r="R9" s="18">
-        <v>0</v>
-      </c>
-      <c r="S9" s="18">
-        <v>0</v>
-      </c>
-      <c r="T9" s="18">
-        <v>0</v>
-      </c>
-      <c r="V9" s="20">
-        <v>10002</v>
-      </c>
-      <c r="W9" s="18">
-        <v>100001</v>
-      </c>
-    </row>
-    <row r="10" ht="57" spans="1:23">
-      <c r="A10" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" s="18">
-        <v>500005</v>
-      </c>
-      <c r="C10" s="18">
-        <v>500005</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="18">
-        <v>500005</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10" s="19">
-        <v>5</v>
-      </c>
-      <c r="H10" s="18">
-        <v>0</v>
-      </c>
-      <c r="I10" s="18">
-        <v>1</v>
-      </c>
-      <c r="J10" s="18">
-        <v>0</v>
-      </c>
-      <c r="K10" s="18">
-        <v>1</v>
-      </c>
-      <c r="L10" s="18">
-        <v>9</v>
-      </c>
-      <c r="M10" s="18">
-        <v>0</v>
-      </c>
-      <c r="N10" s="18">
-        <v>0</v>
-      </c>
-      <c r="O10" s="18">
-        <v>0</v>
-      </c>
-      <c r="P10" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="18">
-        <v>0</v>
-      </c>
-      <c r="R10" s="18">
-        <v>0</v>
-      </c>
-      <c r="S10" s="18">
-        <v>0</v>
-      </c>
-      <c r="T10" s="18">
-        <v>0</v>
-      </c>
-      <c r="V10" s="20">
-        <v>10002</v>
-      </c>
-      <c r="W10" s="18">
-        <v>100001</v>
-      </c>
-    </row>
-    <row r="11" ht="57" spans="1:23">
-      <c r="A11" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" s="18">
-        <v>500006</v>
-      </c>
-      <c r="C11" s="18">
-        <v>500006</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" s="18">
-        <v>500006</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11" s="19">
-        <v>4</v>
-      </c>
-      <c r="H11" s="18">
-        <v>0</v>
-      </c>
-      <c r="I11" s="18">
-        <v>1</v>
-      </c>
-      <c r="J11" s="18">
-        <v>0</v>
-      </c>
-      <c r="K11" s="18">
-        <v>1</v>
-      </c>
-      <c r="L11" s="18">
-        <v>6</v>
-      </c>
-      <c r="M11" s="18">
-        <v>0</v>
-      </c>
-      <c r="N11" s="18">
-        <v>0</v>
-      </c>
-      <c r="O11" s="18">
-        <v>0</v>
-      </c>
-      <c r="P11" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="18">
-        <v>0</v>
-      </c>
-      <c r="R11" s="18">
-        <v>0</v>
-      </c>
-      <c r="S11" s="18">
-        <v>0</v>
-      </c>
-      <c r="T11" s="18">
-        <v>0</v>
-      </c>
-      <c r="V11" s="20">
-        <v>10002</v>
-      </c>
-      <c r="W11" s="18">
-        <v>100001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23">
-      <c r="R12" s="18"/>
-      <c r="S12" s="18"/>
-      <c r="T12" s="18"/>
-    </row>
-    <row r="15" ht="57" spans="1:23">
-      <c r="A15" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" s="18">
-        <v>500007</v>
-      </c>
-      <c r="C15" s="18">
-        <v>500007</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" s="18">
-        <v>500007</v>
-      </c>
-      <c r="F15" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="G15" s="19">
-        <v>4</v>
-      </c>
-      <c r="H15" s="18">
-        <v>0</v>
-      </c>
-      <c r="I15" s="18">
-        <v>1</v>
-      </c>
-      <c r="J15" s="18">
-        <v>0</v>
-      </c>
-      <c r="K15" s="18">
-        <v>1</v>
-      </c>
-      <c r="L15" s="18">
-        <v>6</v>
-      </c>
-      <c r="M15" s="18">
-        <v>0</v>
-      </c>
-      <c r="N15" s="18">
-        <v>0</v>
-      </c>
-      <c r="O15" s="18">
-        <v>0</v>
-      </c>
-      <c r="P15" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="18">
-        <v>0</v>
-      </c>
-      <c r="R15" s="18">
-        <v>0</v>
-      </c>
-      <c r="S15" s="18">
-        <v>0</v>
-      </c>
-      <c r="T15" s="18">
-        <v>0</v>
-      </c>
-      <c r="V15" s="18"/>
-      <c r="W15" s="18">
-        <v>100002</v>
       </c>
     </row>
   </sheetData>
@@ -2062,7 +1707,7 @@
     <mergeCell ref="G1:T1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4 D15 D5:D11">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D7">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>

--- a/Luban/DataTables/Datas/Entity/单位表.xlsx
+++ b/Luban/DataTables/Datas/Entity/单位表.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity\ProjectTinyRpg\Luban\DataTables\Datas\Entity\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="610"/>
+    <workbookView windowWidth="28800" windowHeight="11775" tabRatio="610"/>
   </bookViews>
   <sheets>
     <sheet name="单位表1" sheetId="3" r:id="rId1"/>

--- a/Luban/DataTables/Datas/Entity/单位表.xlsx
+++ b/Luban/DataTables/Datas/Entity/单位表.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11775" tabRatio="610"/>
+    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="610"/>
   </bookViews>
   <sheets>
     <sheet name="单位表1" sheetId="3" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="53">
   <si>
     <t>##</t>
   </si>
@@ -72,15 +72,9 @@
     <t>attr</t>
   </si>
   <si>
-    <t>abilities</t>
-  </si>
-  <si>
     <t>drop_id</t>
   </si>
   <si>
-    <t>ai_id</t>
-  </si>
-  <si>
     <t>单位id</t>
   </si>
   <si>
@@ -136,9 +130,6 @@
   </si>
   <si>
     <t>Dodge</t>
-  </si>
-  <si>
-    <t>技能列表</t>
   </si>
   <si>
     <t>掉落id</t>
@@ -906,7 +897,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -921,24 +912,21 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" textRotation="255"/>
     </xf>
@@ -952,9 +940,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1292,7 +1277,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -1309,10 +1294,9 @@
     <col min="18" max="18" width="16.5166666666667" customWidth="1"/>
     <col min="19" max="19" width="8.90833333333333" customWidth="1"/>
     <col min="20" max="20" width="8.68333333333333" customWidth="1"/>
-    <col min="21" max="21" width="16.5166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:23">
+    <row r="1" s="1" customFormat="1" spans="1:21">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1347,364 +1331,348 @@
       <c r="R1" s="5"/>
       <c r="S1" s="5"/>
       <c r="T1" s="5"/>
-      <c r="U1" s="6" t="s">
+      <c r="U1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="V1" s="1" t="s">
+    </row>
+    <row r="2" ht="58.5" spans="1:21">
+      <c r="A2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="C2" s="7" t="s">
         <v>9</v>
       </c>
+      <c r="D2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="P2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q2" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="T2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="U2" s="11" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" ht="58.5" spans="1:23">
-      <c r="A2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="7" t="s">
+    <row r="3" s="2" customFormat="1" ht="71.25" spans="1:21">
+      <c r="A3" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="O3" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="P3" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q3" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="R3" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="S3" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="T3" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="U3" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" ht="28.5" spans="1:21">
+      <c r="A4" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="16">
+        <v>100001</v>
+      </c>
+      <c r="C4" s="16">
+        <v>100001</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="16">
+        <v>100001</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="17">
+        <v>5</v>
+      </c>
+      <c r="H4" s="16">
+        <v>5</v>
+      </c>
+      <c r="I4" s="16">
+        <v>5</v>
+      </c>
+      <c r="J4" s="16">
+        <v>5</v>
+      </c>
+      <c r="K4" s="16">
+        <v>5</v>
+      </c>
+      <c r="L4" s="16">
+        <v>5</v>
+      </c>
+      <c r="M4" s="16">
         <v>10</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="O2" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="P2" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q2" s="9" t="s">
+      <c r="N4" s="16">
+        <v>0</v>
+      </c>
+      <c r="O4" s="16">
         <v>25</v>
       </c>
-      <c r="R2" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="S2" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="T2" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="U2" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="V2" s="12" t="s">
-        <v>30</v>
+      <c r="P4" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="16">
+        <v>0</v>
+      </c>
+      <c r="R4" s="16">
+        <v>0</v>
+      </c>
+      <c r="S4" s="16">
+        <v>0</v>
+      </c>
+      <c r="T4" s="16">
+        <v>6</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="71.25" spans="1:23">
-      <c r="A3" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K3" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="L3" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="M3" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="N3" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="O3" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="P3" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q3" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="R3" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="S3" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="T3" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="U3" s="17"/>
-      <c r="V3" s="16" t="s">
-        <v>48</v>
-      </c>
+    <row r="5" spans="1:21">
+      <c r="A5" s="18"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="16"/>
+      <c r="T5" s="16"/>
     </row>
-    <row r="4" ht="28.5" spans="1:23">
-      <c r="A4" s="18" t="s">
+    <row r="6" ht="28.5" spans="1:21">
+      <c r="A6" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="18">
-        <v>100001</v>
-      </c>
-      <c r="C4" s="18">
-        <v>100001</v>
-      </c>
-      <c r="D4" s="18" t="s">
+      <c r="B6" s="16">
+        <v>500001</v>
+      </c>
+      <c r="C6" s="16">
+        <v>500001</v>
+      </c>
+      <c r="D6" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="18">
-        <v>100001</v>
-      </c>
-      <c r="F4" s="19" t="s">
+      <c r="E6" s="16">
+        <v>500001</v>
+      </c>
+      <c r="F6" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G6" s="17">
         <v>5</v>
       </c>
-      <c r="H4" s="18">
-        <v>5</v>
-      </c>
-      <c r="I4" s="18">
-        <v>5</v>
-      </c>
-      <c r="J4" s="18">
-        <v>5</v>
-      </c>
-      <c r="K4" s="18">
-        <v>5</v>
-      </c>
-      <c r="L4" s="18">
-        <v>5</v>
-      </c>
-      <c r="M4" s="18">
-        <v>10</v>
-      </c>
-      <c r="N4" s="18">
-        <v>0</v>
-      </c>
-      <c r="O4" s="18">
-        <v>25</v>
-      </c>
-      <c r="P4" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="18">
-        <v>0</v>
-      </c>
-      <c r="R4" s="18">
-        <v>0</v>
-      </c>
-      <c r="S4" s="18">
-        <v>0</v>
-      </c>
-      <c r="T4" s="18">
-        <v>6</v>
+      <c r="H6" s="16">
+        <v>2</v>
+      </c>
+      <c r="I6" s="16">
+        <v>1</v>
+      </c>
+      <c r="J6" s="16">
+        <v>0</v>
+      </c>
+      <c r="K6" s="16">
+        <v>1</v>
+      </c>
+      <c r="L6" s="16">
+        <v>8</v>
+      </c>
+      <c r="M6" s="16">
+        <v>0</v>
+      </c>
+      <c r="N6" s="16">
+        <v>0</v>
+      </c>
+      <c r="O6" s="16">
+        <v>0</v>
+      </c>
+      <c r="P6" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>0</v>
+      </c>
+      <c r="R6" s="16">
+        <v>0</v>
+      </c>
+      <c r="S6" s="16">
+        <v>0</v>
+      </c>
+      <c r="T6" s="16">
+        <v>0</v>
+      </c>
+      <c r="U6" s="18">
+        <v>10002</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
-      <c r="A5" s="20"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
-      <c r="L5" s="18"/>
-      <c r="M5" s="18"/>
-      <c r="N5" s="18"/>
-      <c r="O5" s="18"/>
-      <c r="P5" s="18"/>
-      <c r="Q5" s="18"/>
-      <c r="R5" s="18"/>
-      <c r="S5" s="18"/>
-      <c r="T5" s="18"/>
-    </row>
-    <row r="6" ht="28.5" spans="1:23">
-      <c r="A6" s="20" t="s">
+    <row r="7" ht="28.5" spans="1:21">
+      <c r="A7" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="16">
+        <v>500002</v>
+      </c>
+      <c r="C7" s="16">
+        <v>500002</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="16">
+        <v>500002</v>
+      </c>
+      <c r="F7" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B6" s="18">
-        <v>500001</v>
-      </c>
-      <c r="C6" s="18">
-        <v>500001</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="18">
-        <v>500001</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6" s="19">
-        <v>5</v>
-      </c>
-      <c r="H6" s="18">
+      <c r="G7" s="17">
+        <v>4</v>
+      </c>
+      <c r="H7" s="16">
+        <v>1</v>
+      </c>
+      <c r="I7" s="16">
         <v>2</v>
       </c>
-      <c r="I6" s="18">
+      <c r="J7" s="16">
+        <v>0</v>
+      </c>
+      <c r="K7" s="16">
         <v>1</v>
       </c>
-      <c r="J6" s="18">
-        <v>0</v>
-      </c>
-      <c r="K6" s="18">
-        <v>1</v>
-      </c>
-      <c r="L6" s="18">
-        <v>8</v>
-      </c>
-      <c r="M6" s="18">
-        <v>0</v>
-      </c>
-      <c r="N6" s="18">
-        <v>0</v>
-      </c>
-      <c r="O6" s="18">
-        <v>0</v>
-      </c>
-      <c r="P6" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="18">
-        <v>0</v>
-      </c>
-      <c r="R6" s="18">
-        <v>0</v>
-      </c>
-      <c r="S6" s="18">
-        <v>0</v>
-      </c>
-      <c r="T6" s="18">
-        <v>0</v>
-      </c>
-      <c r="V6" s="20">
+      <c r="L7" s="16">
+        <v>7</v>
+      </c>
+      <c r="M7" s="16">
+        <v>0</v>
+      </c>
+      <c r="N7" s="16">
+        <v>0</v>
+      </c>
+      <c r="O7" s="16">
+        <v>0</v>
+      </c>
+      <c r="P7" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="16">
+        <v>0</v>
+      </c>
+      <c r="R7" s="16">
+        <v>0</v>
+      </c>
+      <c r="S7" s="16">
+        <v>0</v>
+      </c>
+      <c r="T7" s="16">
+        <v>0</v>
+      </c>
+      <c r="U7" s="18">
         <v>10002</v>
-      </c>
-      <c r="W6" s="18">
-        <v>100001</v>
-      </c>
-    </row>
-    <row r="7" ht="28.5" spans="1:23">
-      <c r="A7" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="18">
-        <v>500002</v>
-      </c>
-      <c r="C7" s="18">
-        <v>500002</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" s="18">
-        <v>500002</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7" s="19">
-        <v>4</v>
-      </c>
-      <c r="H7" s="18">
-        <v>1</v>
-      </c>
-      <c r="I7" s="18">
-        <v>2</v>
-      </c>
-      <c r="J7" s="18">
-        <v>0</v>
-      </c>
-      <c r="K7" s="18">
-        <v>1</v>
-      </c>
-      <c r="L7" s="18">
-        <v>7</v>
-      </c>
-      <c r="M7" s="18">
-        <v>0</v>
-      </c>
-      <c r="N7" s="18">
-        <v>0</v>
-      </c>
-      <c r="O7" s="18">
-        <v>0</v>
-      </c>
-      <c r="P7" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="18">
-        <v>0</v>
-      </c>
-      <c r="R7" s="18">
-        <v>0</v>
-      </c>
-      <c r="S7" s="18">
-        <v>0</v>
-      </c>
-      <c r="T7" s="18">
-        <v>0</v>
-      </c>
-      <c r="V7" s="20">
-        <v>10002</v>
-      </c>
-      <c r="W7" s="18">
-        <v>100001</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/DataTables/Datas/Entity/单位表.xlsx
+++ b/Luban/DataTables/Datas/Entity/单位表.xlsx
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="55">
   <si>
     <t>##</t>
   </si>
@@ -130,6 +130,9 @@
   </si>
   <si>
     <t>Dodge</t>
+  </si>
+  <si>
+    <t>ActionSpeed</t>
   </si>
   <si>
     <t>掉落id</t>
@@ -206,6 +209,9 @@
   </si>
   <si>
     <t>闪避</t>
+  </si>
+  <si>
+    <t>速度</t>
   </si>
   <si>
     <t>对应data_drop表</t>
@@ -897,7 +903,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -909,6 +915,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -922,10 +931,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" textRotation="255"/>
@@ -947,6 +956,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1277,7 +1289,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -1296,7 +1308,7 @@
     <col min="20" max="20" width="8.68333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:21">
+    <row r="1" s="1" customFormat="1" spans="1:22">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1315,369 +1327,386 @@
       <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="1" t="s">
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="58.5" spans="1:21">
-      <c r="A2" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="6" t="s">
+    <row r="2" ht="58.5" spans="1:22">
+      <c r="A2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="M2" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="N2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="O2" s="9" t="s">
+      <c r="O2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="P2" s="9" t="s">
+      <c r="P2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="Q2" s="9" t="s">
+      <c r="Q2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="R2" s="8" t="s">
+      <c r="R2" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="S2" s="8" t="s">
+      <c r="S2" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="T2" s="8" t="s">
+      <c r="T2" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="U2" s="11" t="s">
+      <c r="U2" s="10" t="s">
         <v>27</v>
       </c>
+      <c r="V2" s="12" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="71.25" spans="1:21">
-      <c r="A3" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="13" t="s">
+    <row r="3" s="2" customFormat="1" ht="71.25" spans="1:22">
+      <c r="A3" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="C3" s="14"/>
+      <c r="D3" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14" t="s">
+      <c r="E3" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="F3" s="15"/>
+      <c r="G3" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="H3" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="I3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="K3" s="14" t="s">
+      <c r="J3" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="L3" s="14" t="s">
+      <c r="K3" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="M3" s="14" t="s">
+      <c r="L3" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="N3" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="O3" s="15" t="s">
+      <c r="N3" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="P3" s="14" t="s">
+      <c r="O3" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="Q3" s="14" t="s">
+      <c r="P3" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="R3" s="14" t="s">
+      <c r="Q3" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="S3" s="14" t="s">
+      <c r="R3" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="14" t="s">
+      <c r="S3" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="U3" s="15" t="s">
+      <c r="T3" s="15" t="s">
         <v>45</v>
       </c>
+      <c r="U3" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="V3" s="16" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="4" ht="28.5" spans="1:21">
-      <c r="A4" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="16">
+    <row r="4" ht="28.5" spans="1:22">
+      <c r="A4" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="17">
         <v>100001</v>
       </c>
-      <c r="C4" s="16">
+      <c r="C4" s="17">
         <v>100001</v>
       </c>
-      <c r="D4" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="16">
+      <c r="D4" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="17">
         <v>100001</v>
       </c>
-      <c r="F4" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="G4" s="17">
+      <c r="F4" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" s="18">
         <v>5</v>
       </c>
-      <c r="H4" s="16">
+      <c r="H4" s="17">
         <v>5</v>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="17">
         <v>5</v>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="17">
         <v>5</v>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="17">
         <v>5</v>
       </c>
-      <c r="L4" s="16">
+      <c r="L4" s="17">
         <v>5</v>
       </c>
-      <c r="M4" s="16">
+      <c r="M4" s="17">
         <v>10</v>
       </c>
-      <c r="N4" s="16">
-        <v>0</v>
-      </c>
-      <c r="O4" s="16">
+      <c r="N4" s="17">
+        <v>0</v>
+      </c>
+      <c r="O4" s="17">
         <v>25</v>
       </c>
-      <c r="P4" s="16">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="16">
-        <v>0</v>
-      </c>
-      <c r="R4" s="16">
-        <v>0</v>
-      </c>
-      <c r="S4" s="16">
-        <v>0</v>
-      </c>
-      <c r="T4" s="16">
+      <c r="P4" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="17">
+        <v>0</v>
+      </c>
+      <c r="R4" s="17">
+        <v>0</v>
+      </c>
+      <c r="S4" s="17">
+        <v>0</v>
+      </c>
+      <c r="T4" s="17">
         <v>6</v>
       </c>
+      <c r="U4" s="19">
+        <v>2</v>
+      </c>
     </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="18"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="16"/>
-      <c r="S5" s="16"/>
-      <c r="T5" s="16"/>
+    <row r="5" spans="1:22">
+      <c r="A5" s="20"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="17"/>
+      <c r="T5" s="17"/>
+      <c r="U5" s="19"/>
     </row>
-    <row r="6" ht="28.5" spans="1:21">
-      <c r="A6" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="16">
+    <row r="6" ht="28.5" spans="1:22">
+      <c r="A6" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="17">
         <v>500001</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="17">
         <v>500001</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="17">
+        <v>500001</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="18">
+        <v>5</v>
+      </c>
+      <c r="H6" s="17">
+        <v>2</v>
+      </c>
+      <c r="I6" s="17">
+        <v>1</v>
+      </c>
+      <c r="J6" s="17">
+        <v>0</v>
+      </c>
+      <c r="K6" s="17">
+        <v>1</v>
+      </c>
+      <c r="L6" s="17">
         <v>50</v>
       </c>
-      <c r="E6" s="16">
-        <v>500001</v>
-      </c>
-      <c r="F6" s="17" t="s">
+      <c r="M6" s="17">
+        <v>0</v>
+      </c>
+      <c r="N6" s="17">
+        <v>0</v>
+      </c>
+      <c r="O6" s="17">
+        <v>0</v>
+      </c>
+      <c r="P6" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="17">
+        <v>0</v>
+      </c>
+      <c r="R6" s="17">
+        <v>0</v>
+      </c>
+      <c r="S6" s="17">
+        <v>0</v>
+      </c>
+      <c r="T6" s="17">
+        <v>0</v>
+      </c>
+      <c r="U6" s="20">
+        <v>1</v>
+      </c>
+      <c r="V6" s="20">
+        <v>10002</v>
+      </c>
+    </row>
+    <row r="7" ht="28.5" spans="1:22">
+      <c r="A7" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="G6" s="17">
-        <v>5</v>
-      </c>
-      <c r="H6" s="16">
+      <c r="B7" s="17">
+        <v>500002</v>
+      </c>
+      <c r="C7" s="17">
+        <v>500002</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="17">
+        <v>500002</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" s="18">
+        <v>4</v>
+      </c>
+      <c r="H7" s="17">
+        <v>1</v>
+      </c>
+      <c r="I7" s="17">
         <v>2</v>
       </c>
-      <c r="I6" s="16">
+      <c r="J7" s="17">
+        <v>0</v>
+      </c>
+      <c r="K7" s="17">
         <v>1</v>
       </c>
-      <c r="J6" s="16">
-        <v>0</v>
-      </c>
-      <c r="K6" s="16">
-        <v>1</v>
-      </c>
-      <c r="L6" s="16">
-        <v>8</v>
-      </c>
-      <c r="M6" s="16">
-        <v>0</v>
-      </c>
-      <c r="N6" s="16">
-        <v>0</v>
-      </c>
-      <c r="O6" s="16">
-        <v>0</v>
-      </c>
-      <c r="P6" s="16">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="16">
-        <v>0</v>
-      </c>
-      <c r="R6" s="16">
-        <v>0</v>
-      </c>
-      <c r="S6" s="16">
-        <v>0</v>
-      </c>
-      <c r="T6" s="16">
-        <v>0</v>
-      </c>
-      <c r="U6" s="18">
-        <v>10002</v>
-      </c>
-    </row>
-    <row r="7" ht="28.5" spans="1:21">
-      <c r="A7" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="16">
-        <v>500002</v>
-      </c>
-      <c r="C7" s="16">
-        <v>500002</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="16">
-        <v>500002</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="G7" s="17">
-        <v>4</v>
-      </c>
-      <c r="H7" s="16">
-        <v>1</v>
-      </c>
-      <c r="I7" s="16">
-        <v>2</v>
-      </c>
-      <c r="J7" s="16">
-        <v>0</v>
-      </c>
-      <c r="K7" s="16">
-        <v>1</v>
-      </c>
-      <c r="L7" s="16">
+      <c r="L7" s="17">
         <v>7</v>
       </c>
-      <c r="M7" s="16">
-        <v>0</v>
-      </c>
-      <c r="N7" s="16">
-        <v>0</v>
-      </c>
-      <c r="O7" s="16">
-        <v>0</v>
-      </c>
-      <c r="P7" s="16">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="16">
-        <v>0</v>
-      </c>
-      <c r="R7" s="16">
-        <v>0</v>
-      </c>
-      <c r="S7" s="16">
-        <v>0</v>
-      </c>
-      <c r="T7" s="16">
-        <v>0</v>
-      </c>
-      <c r="U7" s="18">
+      <c r="M7" s="17">
+        <v>0</v>
+      </c>
+      <c r="N7" s="17">
+        <v>0</v>
+      </c>
+      <c r="O7" s="17">
+        <v>0</v>
+      </c>
+      <c r="P7" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="17">
+        <v>0</v>
+      </c>
+      <c r="R7" s="17">
+        <v>0</v>
+      </c>
+      <c r="S7" s="17">
+        <v>0</v>
+      </c>
+      <c r="T7" s="17">
+        <v>0</v>
+      </c>
+      <c r="U7" s="20">
+        <v>3</v>
+      </c>
+      <c r="V7" s="20">
         <v>10002</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="G1:T1"/>
+    <mergeCell ref="G1:U1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D7">

--- a/Luban/DataTables/Datas/Entity/单位表.xlsx
+++ b/Luban/DataTables/Datas/Entity/单位表.xlsx
@@ -903,16 +903,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1327,380 +1324,380 @@
       <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
       <c r="V1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="58.5" spans="1:22">
-      <c r="A2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="7" t="s">
+      <c r="A2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="N2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="P2" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="Q2" s="10" t="s">
+      <c r="Q2" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="R2" s="10" t="s">
+      <c r="R2" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="S2" s="10" t="s">
+      <c r="S2" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="T2" s="10" t="s">
+      <c r="T2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="U2" s="10" t="s">
+      <c r="U2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="V2" s="12" t="s">
+      <c r="V2" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" ht="71.25" spans="1:22">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14" t="s">
+      <c r="C3" s="13"/>
+      <c r="D3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="I3" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="J3" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="K3" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="L3" s="15" t="s">
+      <c r="L3" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="N3" s="16" t="s">
+      <c r="N3" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="16" t="s">
+      <c r="O3" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="P3" s="15" t="s">
+      <c r="P3" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="Q3" s="15" t="s">
+      <c r="Q3" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="R3" s="15" t="s">
+      <c r="R3" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="S3" s="15" t="s">
+      <c r="S3" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="T3" s="15" t="s">
+      <c r="T3" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="U3" s="16" t="s">
+      <c r="U3" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="V3" s="16" t="s">
+      <c r="V3" s="15" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="4" ht="28.5" spans="1:22">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="16">
         <v>100001</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="16">
         <v>100001</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="16">
         <v>100001</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="G4" s="18">
+      <c r="G4" s="17">
         <v>5</v>
       </c>
-      <c r="H4" s="17">
+      <c r="H4" s="16">
         <v>5</v>
       </c>
-      <c r="I4" s="17">
+      <c r="I4" s="16">
         <v>5</v>
       </c>
-      <c r="J4" s="17">
+      <c r="J4" s="16">
         <v>5</v>
       </c>
-      <c r="K4" s="17">
+      <c r="K4" s="16">
         <v>5</v>
       </c>
-      <c r="L4" s="17">
+      <c r="L4" s="16">
         <v>5</v>
       </c>
-      <c r="M4" s="17">
+      <c r="M4" s="16">
         <v>10</v>
       </c>
-      <c r="N4" s="17">
-        <v>0</v>
-      </c>
-      <c r="O4" s="17">
+      <c r="N4" s="16">
+        <v>0</v>
+      </c>
+      <c r="O4" s="16">
         <v>25</v>
       </c>
-      <c r="P4" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="17">
-        <v>0</v>
-      </c>
-      <c r="R4" s="17">
-        <v>0</v>
-      </c>
-      <c r="S4" s="17">
-        <v>0</v>
-      </c>
-      <c r="T4" s="17">
+      <c r="P4" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="16">
+        <v>0</v>
+      </c>
+      <c r="R4" s="16">
+        <v>0</v>
+      </c>
+      <c r="S4" s="16">
+        <v>0</v>
+      </c>
+      <c r="T4" s="16">
         <v>6</v>
       </c>
-      <c r="U4" s="19">
+      <c r="U4" s="18">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:22">
-      <c r="A5" s="20"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="17"/>
-      <c r="S5" s="17"/>
-      <c r="T5" s="17"/>
-      <c r="U5" s="19"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="16"/>
+      <c r="T5" s="16"/>
+      <c r="U5" s="18"/>
     </row>
     <row r="6" ht="28.5" spans="1:22">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="16">
         <v>500001</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="16">
         <v>500001</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="16">
         <v>500001</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="17">
         <v>5</v>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="16">
         <v>2</v>
       </c>
-      <c r="I6" s="17">
+      <c r="I6" s="16">
         <v>1</v>
       </c>
-      <c r="J6" s="17">
-        <v>0</v>
-      </c>
-      <c r="K6" s="17">
+      <c r="J6" s="16">
+        <v>0</v>
+      </c>
+      <c r="K6" s="16">
         <v>1</v>
       </c>
-      <c r="L6" s="17">
-        <v>50</v>
-      </c>
-      <c r="M6" s="17">
-        <v>0</v>
-      </c>
-      <c r="N6" s="17">
-        <v>0</v>
-      </c>
-      <c r="O6" s="17">
-        <v>0</v>
-      </c>
-      <c r="P6" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="17">
-        <v>0</v>
-      </c>
-      <c r="R6" s="17">
-        <v>0</v>
-      </c>
-      <c r="S6" s="17">
-        <v>0</v>
-      </c>
-      <c r="T6" s="17">
-        <v>0</v>
-      </c>
-      <c r="U6" s="20">
+      <c r="L6" s="16">
+        <v>20</v>
+      </c>
+      <c r="M6" s="16">
+        <v>0</v>
+      </c>
+      <c r="N6" s="16">
+        <v>0</v>
+      </c>
+      <c r="O6" s="16">
+        <v>0</v>
+      </c>
+      <c r="P6" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>0</v>
+      </c>
+      <c r="R6" s="16">
+        <v>0</v>
+      </c>
+      <c r="S6" s="16">
+        <v>0</v>
+      </c>
+      <c r="T6" s="16">
+        <v>0</v>
+      </c>
+      <c r="U6" s="19">
         <v>1</v>
       </c>
-      <c r="V6" s="20">
+      <c r="V6" s="19">
         <v>10002</v>
       </c>
     </row>
     <row r="7" ht="28.5" spans="1:22">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="16">
         <v>500002</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="16">
         <v>500002</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="16">
         <v>500002</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="17">
         <v>4</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="16">
         <v>1</v>
       </c>
-      <c r="I7" s="17">
+      <c r="I7" s="16">
         <v>2</v>
       </c>
-      <c r="J7" s="17">
-        <v>0</v>
-      </c>
-      <c r="K7" s="17">
+      <c r="J7" s="16">
+        <v>0</v>
+      </c>
+      <c r="K7" s="16">
         <v>1</v>
       </c>
-      <c r="L7" s="17">
+      <c r="L7" s="16">
         <v>7</v>
       </c>
-      <c r="M7" s="17">
-        <v>0</v>
-      </c>
-      <c r="N7" s="17">
-        <v>0</v>
-      </c>
-      <c r="O7" s="17">
-        <v>0</v>
-      </c>
-      <c r="P7" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="17">
-        <v>0</v>
-      </c>
-      <c r="R7" s="17">
-        <v>0</v>
-      </c>
-      <c r="S7" s="17">
-        <v>0</v>
-      </c>
-      <c r="T7" s="17">
-        <v>0</v>
-      </c>
-      <c r="U7" s="20">
+      <c r="M7" s="16">
+        <v>0</v>
+      </c>
+      <c r="N7" s="16">
+        <v>0</v>
+      </c>
+      <c r="O7" s="16">
+        <v>0</v>
+      </c>
+      <c r="P7" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="16">
+        <v>0</v>
+      </c>
+      <c r="R7" s="16">
+        <v>0</v>
+      </c>
+      <c r="S7" s="16">
+        <v>0</v>
+      </c>
+      <c r="T7" s="16">
+        <v>0</v>
+      </c>
+      <c r="U7" s="19">
         <v>3</v>
       </c>
-      <c r="V7" s="20">
+      <c r="V7" s="19">
         <v>10002</v>
       </c>
     </row>
